--- a/docs/lacunas_tecnicos_formacoes_2008_2013.xlsx
+++ b/docs/lacunas_tecnicos_formacoes_2008_2013.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T87"/>
+  <dimension ref="A1:T83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -435,7 +435,7 @@
     <col width="33" customWidth="1" min="16" max="16"/>
     <col width="33" customWidth="1" min="17" max="17"/>
     <col width="34" customWidth="1" min="18" max="18"/>
-    <col width="82" customWidth="1" min="19" max="19"/>
+    <col width="71" customWidth="1" min="19" max="19"/>
     <col width="82" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
@@ -546,73 +546,73 @@
         <v>2008</v>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>2370</v>
+        <v>2464</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2008-06-08</t>
+          <t>2008-07-20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Portuguesa</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Vitoria</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>formacao_mandante, formacao_visitante</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Caio Júnior</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Vagner Mancini</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/909377</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>tecnico_mandante, tecnico_visitante</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/909294</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Caio Júnior</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Vagner Mancini</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -626,29 +626,29 @@
         <v>2008</v>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C3" t="n">
-        <v>2464</v>
+        <v>2530</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2008-07-20</t>
+          <t>2008-08-20</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Sao Paulo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitoria</t>
+          <t>Athletico-PR</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -658,19 +658,19 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Caio Júnior</t>
+          <t>Muricy Ramalho</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Vagner Mancini</t>
+          <t>Mário Sérgio</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/909377</t>
+          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/923049</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -680,19 +680,19 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Caio Júnior</t>
+          <t>Muricy Ramalho</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vagner Mancini</t>
+          <t>Mário Sérgio</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -703,32 +703,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>2530</v>
+        <v>2720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2008-08-20</t>
+          <t>2009-05-17</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sao Paulo</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Athletico-PR</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>3-3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -738,19 +738,19 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Muricy Ramalho</t>
+          <t>Vagner Mancini</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Mário Sérgio</t>
+          <t>Hélio dos Anjos</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/923049</t>
+          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/939079</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -760,19 +760,19 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Muricy Ramalho</t>
+          <t>Vagner Mancini</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mário Sérgio</t>
+          <t>Hélio dos Anjos</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -783,156 +783,132 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B5" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>2679</v>
+        <v>2826</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2008-11-22</t>
+          <t>2009-07-19</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Portuguesa</t>
+          <t>Botafogo-RJ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>tecnico_mandante, tecnico_visitante</t>
+          <t>tecnico_mandante, tecnico_visitante, formacao_mandante, formacao_visitante</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/929585</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Link conhecido; conferir/aplicar somente os campos listados em o_que_falta.</t>
+          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B6" t="n">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="C6" t="n">
-        <v>2689</v>
+        <v>2856</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2008-11-30</t>
+          <t>2009-07-30</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Portuguesa</t>
+          <t>Sao Paulo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Gremio</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>formacao_mandante, formacao_visitante</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Ricardo Gomes</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Paulo Autuori</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/939217</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>tecnico_mandante, tecnico_visitante</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>3-5-2</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/930203</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>3-5-2</t>
-        </is>
-      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Ricardo Gomes</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Paulo Autuori</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -943,32 +919,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B7" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>2702</v>
+        <v>2862</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2008-12-07</t>
+          <t>2009-08-02</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Athletico-PR</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Portuguesa</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -980,17 +956,17 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>4-4-2</t>
+          <t>3-5-2</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>4-4-2</t>
+          <t>3-5-2</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/930213</t>
+          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/939223</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1002,17 +978,17 @@
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>4-4-2</t>
+          <t>3-5-2</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>4-4-2</t>
+          <t>3-5-2</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1026,29 +1002,29 @@
         <v>2009</v>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>2720</v>
+        <v>2908</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2009-05-17</t>
+          <t>2009-08-22</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Santo Andre</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3-3</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1058,19 +1034,19 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Vagner Mancini</t>
+          <t>Alexandre Gallo</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Hélio dos Anjos</t>
+          <t>Ney Franco</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/939079</t>
+          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/965902</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1080,19 +1056,19 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Vagner Mancini</t>
+          <t>Alexandre Gallo</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hélio dos Anjos</t>
+          <t>Ney Franco</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1103,22 +1079,22 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B9" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>2826</v>
+        <v>3099</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2009-07-19</t>
+          <t>2010-05-15</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Botafogo-RJ</t>
+          <t>Vitoria</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1128,107 +1104,131 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>tecnico_mandante, tecnico_visitante, formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>formacao_mandante, formacao_visitante</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Ricardo Silva</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Rogério Lourenço</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1003486</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>tecnico_mandante, tecnico_visitante</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Ricardo Silva</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Rogério Lourenço</t>
+        </is>
+      </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
+          <t>Link conhecido; conferir/aplicar somente os campos listados em o_que_falta.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>2856</v>
+        <v>3223</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2009-07-30</t>
+          <t>2010-08-15</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sao Paulo</t>
+          <t>Gremio Prudente</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gremio</t>
+          <t>Vasco</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Ricardo Gomes</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Paulo Autuori</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+          <t>tecnico_mandante, tecnico_visitante</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>4-4-2</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>4-4-2</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/939217</t>
+          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1006345</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>tecnico_mandante, tecnico_visitante</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Ricardo Gomes</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Paulo Autuori</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
+          <t>formacao_mandante, formacao_visitante</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>4-4-2</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>4-4-2</t>
+        </is>
+      </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1239,32 +1239,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>2862</v>
+        <v>3287</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2009-08-02</t>
+          <t>2010-09-11</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Athletico-PR</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Vitoria</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1276,17 +1276,17 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>3-5-2</t>
+          <t>4-4-2</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>3-5-2</t>
+          <t>4-4-2</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/939223</t>
+          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1007650</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1298,17 +1298,17 @@
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>3-5-2</t>
+          <t>4-4-2</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>3-5-2</t>
+          <t>4-4-2</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -1319,76 +1319,76 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>2908</v>
+        <v>3326</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2009-08-22</t>
+          <t>2010-09-23</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Santo Andre</t>
+          <t>Vitoria</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Alexandre Gallo</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Ney Franco</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+          <t>tecnico_mandante, tecnico_visitante</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>4-4-2</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>4-4-2</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/965902</t>
+          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1009327</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>tecnico_mandante, tecnico_visitante</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Alexandre Gallo</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Ney Franco</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
+          <t>formacao_mandante, formacao_visitante</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>4-4-2</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>4-4-2</t>
+        </is>
+      </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -1402,14 +1402,14 @@
         <v>2010</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C13" t="n">
-        <v>3099</v>
+        <v>3333</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2010-05-15</t>
+          <t>2010-09-26</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1419,56 +1419,56 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Ricardo Silva</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Rogério Lourenço</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+          <t>tecnico_mandante, tecnico_visitante</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>4-4-2</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>4-4-2</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1003486</t>
+          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1009337</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>tecnico_mandante, tecnico_visitante</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Ricardo Silva</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Rogério Lourenço</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
+          <t>formacao_mandante, formacao_visitante</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>4-4-2</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>4-4-2</t>
+        </is>
+      </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -1482,14 +1482,14 @@
         <v>2010</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C14" t="n">
-        <v>3223</v>
+        <v>3340</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2010-08-15</t>
+          <t>2010-09-29</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vasco</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1516,17 +1516,17 @@
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
+          <t>4-5-1</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t>4-4-2</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1006345</t>
+          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1009343</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1538,17 +1538,17 @@
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr">
         <is>
+          <t>4-5-1</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
           <t>4-4-2</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -1562,19 +1562,19 @@
         <v>2010</v>
       </c>
       <c r="B15" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C15" t="n">
-        <v>3287</v>
+        <v>3342</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2010-09-11</t>
+          <t>2010-09-29</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Athletico-PR</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1007650</t>
+          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1009348</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -1642,29 +1642,29 @@
         <v>2010</v>
       </c>
       <c r="B16" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C16" t="n">
-        <v>3326</v>
+        <v>3350</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2010-09-23</t>
+          <t>2010-10-02</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vitoria</t>
+          <t>Gremio Prudente</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1009327</t>
+          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1009353</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -1722,14 +1722,14 @@
         <v>2010</v>
       </c>
       <c r="B17" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C17" t="n">
-        <v>3333</v>
+        <v>3351</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2010-09-26</t>
+          <t>2010-10-02</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1739,12 +1739,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Gremio</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-3</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1009337</t>
+          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1009357</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -1802,29 +1802,29 @@
         <v>2010</v>
       </c>
       <c r="B18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C18" t="n">
-        <v>3340</v>
+        <v>3355</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2010-09-29</t>
+          <t>2010-10-02</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Gremio Prudente</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Sao Paulo</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4-2</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1009343</t>
+          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1009358</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -1882,19 +1882,19 @@
         <v>2010</v>
       </c>
       <c r="B19" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C19" t="n">
-        <v>3342</v>
+        <v>3362</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2010-09-29</t>
+          <t>2010-10-06</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Athletico-PR</t>
+          <t>Sao Paulo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>4-4-2</t>
+          <t>4-5-1</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1009348</t>
+          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1009359</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>4-4-2</t>
+          <t>4-5-1</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -1962,24 +1962,24 @@
         <v>2010</v>
       </c>
       <c r="B20" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C20" t="n">
-        <v>3350</v>
+        <v>3443</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2010-10-02</t>
+          <t>2010-11-21</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Gremio Prudente</t>
+          <t>Vitoria</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1989,46 +1989,46 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
+          <t>formacao_mandante, formacao_visitante</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Antônio Lopes</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Tite</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1009448</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
           <t>tecnico_mandante, tecnico_visitante</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1009353</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Antônio Lopes</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Tite</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -2042,73 +2042,73 @@
         <v>2010</v>
       </c>
       <c r="B21" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>3351</v>
+        <v>3445</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2010-10-02</t>
+          <t>2010-11-21</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vitoria</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gremio</t>
+          <t>Atletico-GO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
+          <t>formacao_mandante, formacao_visitante</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Vágner Benazzi</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Renê Simões</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1009449</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
           <t>tecnico_mandante, tecnico_visitante</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1009357</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Vágner Benazzi</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Renê Simões</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -2122,14 +2122,14 @@
         <v>2010</v>
       </c>
       <c r="B22" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="C22" t="n">
-        <v>3355</v>
+        <v>3456</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2010-10-02</t>
+          <t>2010-11-28</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2139,56 +2139,56 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sao Paulo</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
+          <t>formacao_mandante, formacao_visitante</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Vágner Benazzi</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Marcelo Martelotte</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1009459</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
           <t>tecnico_mandante, tecnico_visitante</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>4-5-1</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1009358</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>4-5-1</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Vágner Benazzi</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Marcelo Martelotte</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -2202,73 +2202,73 @@
         <v>2010</v>
       </c>
       <c r="B23" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C23" t="n">
-        <v>3362</v>
+        <v>3466</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2010-10-06</t>
+          <t>2010-12-05</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sao Paulo</t>
+          <t>Vitoria</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitoria</t>
+          <t>Atletico-GO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
+          <t>formacao_mandante, formacao_visitante</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Antônio Lopes</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Renê Simões</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1009468</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
           <t>tecnico_mandante, tecnico_visitante</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>4-5-1</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1009359</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>4-5-1</t>
-        </is>
-      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Antônio Lopes</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Renê Simões</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -2279,32 +2279,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B24" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>3443</v>
+        <v>3467</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2010-11-21</t>
+          <t>2011-05-21</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vitoria</t>
+          <t>Atletico-MG</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Athletico-PR</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2314,19 +2314,19 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Antônio Lopes</t>
+          <t>Dorival Júnior</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Tite</t>
+          <t>Adilson Batista</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1009448</t>
+          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1091614</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2336,19 +2336,19 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Antônio Lopes</t>
+          <t>Dorival Júnior</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Tite</t>
+          <t>Adilson Batista</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
@@ -2359,32 +2359,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B25" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>3445</v>
+        <v>3504</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2010-11-21</t>
+          <t>2011-06-12</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Atletico-GO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Atletico-GO</t>
+          <t>Ceara</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2394,19 +2394,19 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Vágner Benazzi</t>
+          <t>Paulo César Gusmão</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Renê Simões</t>
+          <t>Vagner Mancini</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1009449</t>
+          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1093666</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2416,19 +2416,19 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Vágner Benazzi</t>
+          <t>Paulo César Gusmão</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Renê Simões</t>
+          <t>Vagner Mancini</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
@@ -2439,76 +2439,76 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B26" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="C26" t="n">
-        <v>3456</v>
+        <v>3535</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2010-11-28</t>
+          <t>2011-06-30</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Athletico-PR</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Vágner Benazzi</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Marcelo Martelotte</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+          <t>tecnico_mandante, tecnico_visitante</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>4-5-1</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>4-5-1</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1009459</t>
+          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1093700</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>tecnico_mandante, tecnico_visitante</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Vágner Benazzi</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Marcelo Martelotte</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
+          <t>formacao_mandante, formacao_visitante</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>4-5-1</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>4-5-1</t>
+        </is>
+      </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
@@ -2519,76 +2519,76 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B27" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C27" t="n">
-        <v>3466</v>
+        <v>3548</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2010-12-05</t>
+          <t>2011-07-09</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vitoria</t>
+          <t>Sao Paulo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atletico-GO</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Antônio Lopes</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Renê Simões</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+          <t>tecnico_mandante, tecnico_visitante</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>4-5-1</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>4-4-2</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1009468</t>
+          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1093712</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>tecnico_mandante, tecnico_visitante</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>Antônio Lopes</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Renê Simões</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
+          <t>formacao_mandante, formacao_visitante</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>4-5-1</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>4-4-2</t>
+        </is>
+      </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
@@ -2602,73 +2602,73 @@
         <v>2011</v>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C28" t="n">
-        <v>3467</v>
+        <v>3577</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2011-05-21</t>
+          <t>2011-07-21</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Atletico-MG</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Athletico-PR</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Dorival Júnior</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Adilson Batista</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+          <t>tecnico_mandante, tecnico_visitante</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>3-5-2</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>4-4-2</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1091614</t>
+          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1093734</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>tecnico_mandante, tecnico_visitante</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>Dorival Júnior</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Adilson Batista</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
+          <t>formacao_mandante, formacao_visitante</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>3-5-2</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>4-4-2</t>
+        </is>
+      </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
@@ -2682,29 +2682,29 @@
         <v>2011</v>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C29" t="n">
-        <v>3504</v>
+        <v>3579</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2011-06-12</t>
+          <t>2011-07-23</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Atletico-GO</t>
+          <t>Athletico-PR</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ceara</t>
+          <t>Botafogo-RJ</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2714,19 +2714,19 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Paulo César Gusmão</t>
+          <t>Renato Gaúcho</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Vagner Mancini</t>
+          <t>Caio Júnior</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1093666</t>
+          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1093731</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2736,19 +2736,19 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Paulo César Gusmão</t>
+          <t>Renato Gaúcho</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Vagner Mancini</t>
+          <t>Caio Júnior</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
@@ -2762,29 +2762,29 @@
         <v>2011</v>
       </c>
       <c r="B30" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C30" t="n">
-        <v>3535</v>
+        <v>3592</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2011-06-30</t>
+          <t>2011-07-31</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Athletico-PR</t>
+          <t>Atletico-GO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2801,12 +2801,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>4-5-1</t>
+          <t>4-4-2</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1093700</t>
+          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1093757</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>4-5-1</t>
+          <t>4-4-2</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
@@ -2842,24 +2842,24 @@
         <v>2011</v>
       </c>
       <c r="B31" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C31" t="n">
-        <v>3548</v>
+        <v>3614</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2011-07-09</t>
+          <t>2011-08-07</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sao Paulo</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Atletico-GO</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2876,7 +2876,7 @@
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>4-5-1</t>
+          <t>4-4-2</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1093712</t>
+          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1093780</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2898,7 +2898,7 @@
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>4-5-1</t>
+          <t>4-4-2</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
@@ -2922,29 +2922,29 @@
         <v>2011</v>
       </c>
       <c r="B32" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C32" t="n">
-        <v>3577</v>
+        <v>3618</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2011-07-21</t>
+          <t>2011-08-13</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Atletico-GO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2956,7 +2956,7 @@
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>3-5-2</t>
+          <t>4-4-2</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1093734</t>
+          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1093782</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2978,7 +2978,7 @@
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>3-5-2</t>
+          <t>4-4-2</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
@@ -3002,73 +3002,73 @@
         <v>2011</v>
       </c>
       <c r="B33" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C33" t="n">
-        <v>3579</v>
+        <v>3772</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2011-07-23</t>
+          <t>2011-10-23</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Athletico-PR</t>
+          <t>Sao Paulo</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Botafogo-RJ</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Renato Gaúcho</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Caio Júnior</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
+          <t>tecnico_mandante, tecnico_visitante</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>4-4-2</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>4-4-2</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1093731</t>
+          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1158419</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>tecnico_mandante, tecnico_visitante</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>Renato Gaúcho</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Caio Júnior</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
+          <t>formacao_mandante, formacao_visitante</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>4-4-2</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>4-4-2</t>
+        </is>
+      </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
@@ -3082,73 +3082,73 @@
         <v>2011</v>
       </c>
       <c r="B34" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C34" t="n">
-        <v>3592</v>
+        <v>3804</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2011-07-31</t>
+          <t>2011-11-13</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Vasco</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Atletico-GO</t>
+          <t>Botafogo-RJ</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
+          <t>formacao_mandante, formacao_visitante</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Cristóvão Borges</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Caio Júnior</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1164795</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
           <t>tecnico_mandante, tecnico_visitante</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>4-5-1</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1093757</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>4-5-1</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Cristóvão Borges</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Caio Júnior</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
@@ -3159,32 +3159,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="B35" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="C35" t="n">
-        <v>3614</v>
+        <v>4223</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2011-08-07</t>
+          <t>2012-12-02</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Atletico-GO</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3196,17 +3196,17 @@
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>4-4-2</t>
+          <t>4-2-3-1</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>4-4-2</t>
+          <t>4-4-2 duplo 6</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1093780</t>
+          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/2206691</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3218,17 +3218,17 @@
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>4-4-2</t>
+          <t>4-2-3-1</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>4-4-2</t>
+          <t>4-4-2 duplo 6</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
@@ -3239,107 +3239,91 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="B36" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C36" t="n">
-        <v>3618</v>
+        <v>4498</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2011-08-13</t>
+          <t>2013-10-12</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Atletico-GO</t>
+          <t>Vitoria</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>tecnico_mandante, tecnico_visitante</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1093782</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
+          <t>formacao_mandante, formacao_visitante</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Ney Franco</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Péricles Chamusca</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>Link conhecido; conferir/aplicar somente os campos listados em o_que_falta.</t>
+          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="B37" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C37" t="n">
-        <v>3772</v>
+        <v>4508</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2011-10-23</t>
+          <t>2013-10-16</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sao Paulo</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3356,204 +3340,156 @@
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>4-4-2</t>
+          <t>4-3-3 defensivo</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1158419</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
+          <t>4-5-1</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>Link conhecido; conferir/aplicar somente os campos listados em o_que_falta.</t>
+          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="B38" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C38" t="n">
-        <v>3804</v>
+        <v>4509</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2011-11-13</t>
+          <t>2013-10-16</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vasco</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Botafogo-RJ</t>
+          <t>Portuguesa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Cristóvão Borges</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Caio Júnior</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1164795</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
           <t>tecnico_mandante, tecnico_visitante</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>Cristóvão Borges</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Caio Júnior</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>4-1-3-2</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>4-4-2 duplo 6</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>Link conhecido; conferir/aplicar somente os campos listados em o_que_falta.</t>
+          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="B39" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C39" t="n">
-        <v>4223</v>
+        <v>4516</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2012-12-02</t>
+          <t>2013-10-17</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Vitoria</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Botafogo-RJ</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>tecnico_mandante, tecnico_visitante</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>4-2-3-1</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>4-4-2 duplo 6</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/2206691</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
+          <t>formacao_mandante, formacao_visitante</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Ney Franco</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Oswaldo de Oliveira</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>4-2-3-1</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>4-4-2 duplo 6</t>
-        </is>
-      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>Link conhecido; conferir/aplicar somente os campos listados em o_que_falta.</t>
+          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
         </is>
       </c>
     </row>
@@ -3562,29 +3498,29 @@
         <v>2013</v>
       </c>
       <c r="B40" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C40" t="n">
-        <v>4498</v>
+        <v>4521</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2013-10-12</t>
+          <t>2013-10-20</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vitoria</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Sao Paulo</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3594,12 +3530,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Ney Franco</t>
+          <t>Cristóvão Borges</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Péricles Chamusca</t>
+          <t>Muricy Ramalho</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -3612,7 +3548,7 @@
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
@@ -3626,48 +3562,48 @@
         <v>2013</v>
       </c>
       <c r="B41" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C41" t="n">
-        <v>4508</v>
+        <v>4522</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2013-10-16</t>
+          <t>2013-10-20</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Athletico-PR</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>tecnico_mandante, tecnico_visitante</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>4-3-3 defensivo</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>4-5-1</t>
-        </is>
-      </c>
+          <t>formacao_mandante, formacao_visitante</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Enderson Moreira</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Vagner Mancini</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
@@ -3676,7 +3612,7 @@
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
@@ -3690,48 +3626,48 @@
         <v>2013</v>
       </c>
       <c r="B42" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C42" t="n">
-        <v>4509</v>
+        <v>4524</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2013-10-16</t>
+          <t>2013-10-20</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Botafogo-RJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Portuguesa</t>
+          <t>Vasco</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>tecnico_mandante, tecnico_visitante</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>4-1-3-2</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>4-4-2 duplo 6</t>
-        </is>
-      </c>
+          <t>formacao_mandante, formacao_visitante</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Oswaldo de Oliveira</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Dorival Júnior</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
@@ -3740,7 +3676,7 @@
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
@@ -3754,29 +3690,29 @@
         <v>2013</v>
       </c>
       <c r="B43" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C43" t="n">
-        <v>4516</v>
+        <v>4525</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2013-10-17</t>
+          <t>2013-10-20</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vitoria</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Botafogo-RJ</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3786,12 +3722,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Ney Franco</t>
+          <t>Péricles Chamusca</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Oswaldo de Oliveira</t>
+          <t>Marcelo Oliveira</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3804,7 +3740,7 @@
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
@@ -3818,29 +3754,29 @@
         <v>2013</v>
       </c>
       <c r="B44" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C44" t="n">
-        <v>4521</v>
+        <v>4527</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2013-10-20</t>
+          <t>2013-10-26</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Botafogo-RJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sao Paulo</t>
+          <t>Atletico-MG</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3850,12 +3786,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Cristóvão Borges</t>
+          <t>Oswaldo de Oliveira</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Muricy Ramalho</t>
+          <t>Cuca</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3868,7 +3804,7 @@
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
@@ -3882,29 +3818,29 @@
         <v>2013</v>
       </c>
       <c r="B45" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C45" t="n">
-        <v>4522</v>
+        <v>4528</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2013-10-20</t>
+          <t>2013-10-26</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Athletico-PR</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>5-3</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3914,12 +3850,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Enderson Moreira</t>
+          <t>Marcelo Oliveira</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Vagner Mancini</t>
+          <t>Argel Fuchs</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3932,7 +3868,7 @@
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
@@ -3946,29 +3882,29 @@
         <v>2013</v>
       </c>
       <c r="B46" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C46" t="n">
-        <v>4524</v>
+        <v>4529</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2013-10-20</t>
+          <t>2013-10-27</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Botafogo-RJ</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vasco</t>
+          <t>Athletico-PR</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3978,12 +3914,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Oswaldo de Oliveira</t>
+          <t>Cristóvão Borges</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Dorival Júnior</t>
+          <t>Vagner Mancini</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3996,7 +3932,7 @@
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
@@ -4010,29 +3946,29 @@
         <v>2013</v>
       </c>
       <c r="B47" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C47" t="n">
-        <v>4525</v>
+        <v>4531</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2013-10-20</t>
+          <t>2013-10-27</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Sao Paulo</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4042,12 +3978,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Péricles Chamusca</t>
+          <t>Clemer</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Marcelo Oliveira</t>
+          <t>Muricy Ramalho</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -4060,7 +3996,7 @@
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
@@ -4077,26 +4013,26 @@
         <v>31</v>
       </c>
       <c r="C48" t="n">
-        <v>4527</v>
+        <v>4533</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2013-10-26</t>
+          <t>2013-10-27</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Botafogo-RJ</t>
+          <t>Portuguesa</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Atletico-MG</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4106,12 +4042,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Oswaldo de Oliveira</t>
+          <t>Guto Ferreira</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Cuca</t>
+          <t>Jayme de Almeida Filho</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -4124,7 +4060,7 @@
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
@@ -4141,26 +4077,26 @@
         <v>31</v>
       </c>
       <c r="C49" t="n">
-        <v>4528</v>
+        <v>4535</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2013-10-26</t>
+          <t>2013-10-27</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Vitoria</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>5-3</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4170,12 +4106,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Marcelo Oliveira</t>
+          <t>Vanderlei Luxemburgo</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Argel Fuchs</t>
+          <t>Ney Franco</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -4188,7 +4124,7 @@
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
@@ -4205,7 +4141,7 @@
         <v>31</v>
       </c>
       <c r="C50" t="n">
-        <v>4529</v>
+        <v>4536</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4214,17 +4150,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Nautico</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Athletico-PR</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4234,12 +4170,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Cristóvão Borges</t>
+          <t>Marcelo Martelotte</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Vagner Mancini</t>
+          <t>Enderson Moreira</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -4252,7 +4188,7 @@
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
@@ -4266,29 +4202,29 @@
         <v>2013</v>
       </c>
       <c r="B51" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C51" t="n">
-        <v>4531</v>
+        <v>4537</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2013-10-27</t>
+          <t>2013-11-02</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Sao Paulo</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sao Paulo</t>
+          <t>Portuguesa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4298,12 +4234,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Clemer</t>
+          <t>Muricy Ramalho</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Muricy Ramalho</t>
+          <t>Guto Ferreira</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -4316,7 +4252,7 @@
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
@@ -4330,29 +4266,29 @@
         <v>2013</v>
       </c>
       <c r="B52" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C52" t="n">
-        <v>4533</v>
+        <v>4538</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2013-10-27</t>
+          <t>2013-11-02</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Portuguesa</t>
+          <t>Vasco</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4362,12 +4298,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Guto Ferreira</t>
+          <t>Adilson Batista</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Jayme de Almeida Filho</t>
+          <t>Péricles Chamusca</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -4380,7 +4316,7 @@
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
@@ -4394,29 +4330,29 @@
         <v>2013</v>
       </c>
       <c r="B53" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C53" t="n">
-        <v>4535</v>
+        <v>4539</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2013-10-27</t>
+          <t>2013-11-02</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atletico-MG</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitoria</t>
+          <t>Nautico</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4426,12 +4362,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Vanderlei Luxemburgo</t>
+          <t>Cuca</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Ney Franco</t>
+          <t>Marcelo Martelotte</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -4444,7 +4380,7 @@
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
@@ -4458,29 +4394,29 @@
         <v>2013</v>
       </c>
       <c r="B54" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C54" t="n">
-        <v>4536</v>
+        <v>4540</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2013-10-27</t>
+          <t>2013-11-03</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Nautico</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Botafogo-RJ</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4490,12 +4426,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Marcelo Martelotte</t>
+          <t>Enderson Moreira</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Enderson Moreira</t>
+          <t>Oswaldo de Oliveira</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -4508,7 +4444,7 @@
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
@@ -4525,26 +4461,26 @@
         <v>32</v>
       </c>
       <c r="C55" t="n">
-        <v>4537</v>
+        <v>4542</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2013-11-02</t>
+          <t>2013-11-03</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sao Paulo</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Portuguesa</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4554,12 +4490,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Muricy Ramalho</t>
+          <t>Claudinei Oliveira</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Guto Ferreira</t>
+          <t>Marcelo Oliveira</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -4572,7 +4508,7 @@
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
@@ -4589,26 +4525,26 @@
         <v>32</v>
       </c>
       <c r="C56" t="n">
-        <v>4538</v>
+        <v>4543</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2013-11-02</t>
+          <t>2013-11-03</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Vasco</t>
+          <t>Vitoria</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4618,12 +4554,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Adilson Batista</t>
+          <t>Ney Franco</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Péricles Chamusca</t>
+          <t>Tite</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -4636,7 +4572,7 @@
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
@@ -4653,26 +4589,26 @@
         <v>32</v>
       </c>
       <c r="C57" t="n">
-        <v>4539</v>
+        <v>4544</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2013-11-02</t>
+          <t>2013-11-03</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Atletico-MG</t>
+          <t>Athletico-PR</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nautico</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4682,12 +4618,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Cuca</t>
+          <t>Vagner Mancini</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Marcelo Martelotte</t>
+          <t>Clemer</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -4700,7 +4636,7 @@
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
@@ -4717,7 +4653,7 @@
         <v>32</v>
       </c>
       <c r="C58" t="n">
-        <v>4540</v>
+        <v>4545</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4726,17 +4662,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Botafogo-RJ</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4746,12 +4682,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Enderson Moreira</t>
+          <t>Argel Fuchs</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Oswaldo de Oliveira</t>
+          <t>Jorginho</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -4764,7 +4700,7 @@
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
@@ -4781,7 +4717,7 @@
         <v>32</v>
       </c>
       <c r="C59" t="n">
-        <v>4542</v>
+        <v>4546</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4790,17 +4726,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4810,12 +4746,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Claudinei Oliveira</t>
+          <t>Jayme de Almeida Filho</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Marcelo Oliveira</t>
+          <t>Vanderlei Luxemburgo</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4828,7 +4764,7 @@
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
@@ -4842,29 +4778,29 @@
         <v>2013</v>
       </c>
       <c r="B60" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C60" t="n">
-        <v>4543</v>
+        <v>4557</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2013-11-03</t>
+          <t>2013-11-13</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Vitoria</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4874,12 +4810,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Ney Franco</t>
+          <t>Enderson Moreira</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Tite</t>
+          <t>Jorginho</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4892,7 +4828,7 @@
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
@@ -4906,29 +4842,29 @@
         <v>2013</v>
       </c>
       <c r="B61" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C61" t="n">
-        <v>4544</v>
+        <v>4559</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2013-11-03</t>
+          <t>2013-11-13</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Athletico-PR</t>
+          <t>Botafogo-RJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Portuguesa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4938,12 +4874,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Vagner Mancini</t>
+          <t>Oswaldo de Oliveira</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Clemer</t>
+          <t>Guto Ferreira</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4956,7 +4892,7 @@
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
@@ -4970,14 +4906,14 @@
         <v>2013</v>
       </c>
       <c r="B62" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C62" t="n">
-        <v>4545</v>
+        <v>4560</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2013-11-03</t>
+          <t>2013-11-13</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4987,12 +4923,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Athletico-PR</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5007,7 +4943,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Jorginho</t>
+          <t>Vagner Mancini</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -5020,7 +4956,7 @@
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
@@ -5034,29 +4970,29 @@
         <v>2013</v>
       </c>
       <c r="B63" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C63" t="n">
-        <v>4546</v>
+        <v>4561</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2013-11-03</t>
+          <t>2013-11-13</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5066,12 +5002,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Jayme de Almeida Filho</t>
+          <t>Péricles Chamusca</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Vanderlei Luxemburgo</t>
+          <t>Tite</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -5084,7 +5020,7 @@
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
@@ -5101,7 +5037,7 @@
         <v>34</v>
       </c>
       <c r="C64" t="n">
-        <v>4557</v>
+        <v>4562</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5110,12 +5046,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Sao Paulo</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5130,12 +5066,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Enderson Moreira</t>
+          <t>Muricy Ramalho</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Jorginho</t>
+          <t>Jayme de Almeida Filho</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -5148,7 +5084,7 @@
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
@@ -5165,7 +5101,7 @@
         <v>34</v>
       </c>
       <c r="C65" t="n">
-        <v>4559</v>
+        <v>4563</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5174,17 +5110,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Botafogo-RJ</t>
+          <t>Vitoria</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Portuguesa</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5194,12 +5130,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Oswaldo de Oliveira</t>
+          <t>Ney Franco</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Guto Ferreira</t>
+          <t>Marcelo Oliveira</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -5212,7 +5148,7 @@
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
@@ -5229,26 +5165,26 @@
         <v>34</v>
       </c>
       <c r="C66" t="n">
-        <v>4560</v>
+        <v>4564</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2013-11-13</t>
+          <t>2013-11-14</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Athletico-PR</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5258,12 +5194,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Argel Fuchs</t>
+          <t>Claudinei Oliveira</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Vagner Mancini</t>
+          <t>Cristóvão Borges</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -5276,7 +5212,7 @@
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
@@ -5293,26 +5229,26 @@
         <v>34</v>
       </c>
       <c r="C67" t="n">
-        <v>4561</v>
+        <v>4565</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2013-11-13</t>
+          <t>2013-11-14</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Atletico-MG</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5322,12 +5258,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Péricles Chamusca</t>
+          <t>Cuca</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Tite</t>
+          <t>Clemer</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -5340,7 +5276,7 @@
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
@@ -5357,21 +5293,21 @@
         <v>34</v>
       </c>
       <c r="C68" t="n">
-        <v>4562</v>
+        <v>4566</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2013-11-13</t>
+          <t>2013-11-14</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sao Paulo</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Nautico</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5386,12 +5322,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Muricy Ramalho</t>
+          <t>Dorival Júnior</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Jayme de Almeida Filho</t>
+          <t>Marcelo Martelotte</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -5404,7 +5340,7 @@
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
@@ -5418,29 +5354,29 @@
         <v>2013</v>
       </c>
       <c r="B69" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C69" t="n">
-        <v>4563</v>
+        <v>4567</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2013-11-13</t>
+          <t>2013-11-16</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Vitoria</t>
+          <t>Botafogo-RJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Athletico-PR</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>4-0</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5450,12 +5386,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Ney Franco</t>
+          <t>Oswaldo de Oliveira</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Marcelo Oliveira</t>
+          <t>Vagner Mancini</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -5468,7 +5404,7 @@
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
@@ -5482,29 +5418,29 @@
         <v>2013</v>
       </c>
       <c r="B70" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C70" t="n">
-        <v>4564</v>
+        <v>4568</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2013-11-14</t>
+          <t>2013-11-16</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5514,12 +5450,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Claudinei Oliveira</t>
+          <t>Péricles Chamusca</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Cristóvão Borges</t>
+          <t>Argel Fuchs</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -5532,7 +5468,7 @@
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
@@ -5546,29 +5482,29 @@
         <v>2013</v>
       </c>
       <c r="B71" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C71" t="n">
-        <v>4565</v>
+        <v>4569</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2013-11-14</t>
+          <t>2013-11-17</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Atletico-MG</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Vasco</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5578,12 +5514,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Cuca</t>
+          <t>Tite</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Clemer</t>
+          <t>Adilson Batista</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -5596,7 +5532,7 @@
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
@@ -5610,29 +5546,29 @@
         <v>2013</v>
       </c>
       <c r="B72" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C72" t="n">
-        <v>4566</v>
+        <v>4570</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2013-11-14</t>
+          <t>2013-11-17</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nautico</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5642,12 +5578,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Dorival Júnior</t>
+          <t>Marcelo Oliveira</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Marcelo Martelotte</t>
+          <t>Jorginho</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -5660,7 +5596,7 @@
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
@@ -5677,26 +5613,26 @@
         <v>35</v>
       </c>
       <c r="C73" t="n">
-        <v>4567</v>
+        <v>4571</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2013-11-16</t>
+          <t>2013-11-17</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Botafogo-RJ</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Athletico-PR</t>
+          <t>Sao Paulo</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>4-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5706,12 +5642,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Oswaldo de Oliveira</t>
+          <t>Dorival Júnior</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Vagner Mancini</t>
+          <t>Muricy Ramalho</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -5724,7 +5660,7 @@
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
@@ -5741,26 +5677,26 @@
         <v>35</v>
       </c>
       <c r="C74" t="n">
-        <v>4568</v>
+        <v>4572</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2013-11-16</t>
+          <t>2013-11-17</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Vitoria</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5770,12 +5706,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Péricles Chamusca</t>
+          <t>Ney Franco</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Argel Fuchs</t>
+          <t>Claudinei Oliveira</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -5788,7 +5724,7 @@
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
@@ -5805,7 +5741,7 @@
         <v>35</v>
       </c>
       <c r="C75" t="n">
-        <v>4569</v>
+        <v>4573</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5814,17 +5750,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vasco</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5834,12 +5770,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Tite</t>
+          <t>Enderson Moreira</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Adilson Batista</t>
+          <t>Clemer</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5852,7 +5788,7 @@
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
@@ -5869,7 +5805,7 @@
         <v>35</v>
       </c>
       <c r="C76" t="n">
-        <v>4570</v>
+        <v>4575</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5878,17 +5814,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Nautico</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5898,12 +5834,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Marcelo Oliveira</t>
+          <t>Marcelo Martelotte</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Jorginho</t>
+          <t>Cristóvão Borges</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5916,7 +5852,7 @@
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
@@ -5933,7 +5869,7 @@
         <v>35</v>
       </c>
       <c r="C77" t="n">
-        <v>4571</v>
+        <v>4576</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5942,17 +5878,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Portuguesa</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sao Paulo</t>
+          <t>Atletico-MG</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5962,12 +5898,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Dorival Júnior</t>
+          <t>Guto Ferreira</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Muricy Ramalho</t>
+          <t>Cuca</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5980,7 +5916,7 @@
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
@@ -5994,29 +5930,29 @@
         <v>2013</v>
       </c>
       <c r="B78" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C78" t="n">
-        <v>4572</v>
+        <v>4577</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2013-11-17</t>
+          <t>2013-11-23</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
+          <t>Criciuma</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
           <t>Vitoria</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Santos</t>
-        </is>
-      </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -6026,12 +5962,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
+          <t>Argel Fuchs</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
           <t>Ney Franco</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>Claudinei Oliveira</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -6044,7 +5980,7 @@
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
@@ -6058,29 +5994,29 @@
         <v>2013</v>
       </c>
       <c r="B79" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C79" t="n">
-        <v>4573</v>
+        <v>4578</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2013-11-17</t>
+          <t>2013-11-23</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Vasco</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6090,12 +6026,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Enderson Moreira</t>
+          <t>Adilson Batista</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Clemer</t>
+          <t>Marcelo Oliveira</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -6108,7 +6044,7 @@
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
@@ -6122,29 +6058,29 @@
         <v>2013</v>
       </c>
       <c r="B80" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C80" t="n">
-        <v>4575</v>
+        <v>4580</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2013-11-17</t>
+          <t>2013-11-24</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
+          <t>Athletico-PR</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
           <t>Nautico</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Bahia</t>
-        </is>
-      </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>6-1</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -6154,12 +6090,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
+          <t>Vagner Mancini</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
           <t>Marcelo Martelotte</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>Cristóvão Borges</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -6172,7 +6108,7 @@
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
@@ -6186,29 +6122,29 @@
         <v>2013</v>
       </c>
       <c r="B81" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C81" t="n">
-        <v>4576</v>
+        <v>4590</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2013-11-17</t>
+          <t>2013-12-01</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Portuguesa</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Atletico-MG</t>
+          <t>Sao Paulo</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -6218,12 +6154,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Guto Ferreira</t>
+          <t>Argel Fuchs</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Cuca</t>
+          <t>Muricy Ramalho</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -6236,7 +6172,7 @@
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
@@ -6250,29 +6186,29 @@
         <v>2013</v>
       </c>
       <c r="B82" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C82" t="n">
-        <v>4577</v>
+        <v>4591</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2013-11-23</t>
+          <t>2013-12-01</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vitoria</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -6282,12 +6218,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Argel Fuchs</t>
+          <t>Marcelo Oliveira</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Ney Franco</t>
+          <t>Cristóvão Borges</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -6300,7 +6236,7 @@
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
@@ -6314,29 +6250,29 @@
         <v>2013</v>
       </c>
       <c r="B83" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C83" t="n">
-        <v>4578</v>
+        <v>4594</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2013-11-23</t>
+          <t>2013-12-01</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Vasco</t>
+          <t>Vitoria</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -6346,12 +6282,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Adilson Batista</t>
+          <t>Ney Franco</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Marcelo Oliveira</t>
+          <t>Jayme de Almeida Filho</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -6364,266 +6300,10 @@
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr">
         <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
-        <is>
-          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B84" t="n">
-        <v>36</v>
-      </c>
-      <c r="C84" t="n">
-        <v>4580</v>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>2013-11-24</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Athletico-PR</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Nautico</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>6-1</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>Vagner Mancini</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>Marcelo Martelotte</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr"/>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
-        </is>
-      </c>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B85" t="n">
-        <v>37</v>
-      </c>
-      <c r="C85" t="n">
-        <v>4590</v>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>2013-12-01</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Criciuma</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>Argel Fuchs</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>Muricy Ramalho</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr"/>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
-        </is>
-      </c>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B86" t="n">
-        <v>37</v>
-      </c>
-      <c r="C86" t="n">
-        <v>4591</v>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>2013-12-01</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Cruzeiro</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Bahia</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>1-2</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>Marcelo Oliveira</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>Cristóvão Borges</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr"/>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
-        </is>
-      </c>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B87" t="n">
-        <v>37</v>
-      </c>
-      <c r="C87" t="n">
-        <v>4594</v>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>2013-12-01</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Vitoria</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Flamengo</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>4-2</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>Ney Franco</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>Jayme de Almeida Filho</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr"/>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>Transfermarkt buscar por jogo; ogol se Transfermarkt nao trouxer tecnico/formacao; ESPN/arquivo local como fallback</t>
-        </is>
-      </c>
-      <c r="T87" t="inlineStr">
         <is>
           <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
         </is>
@@ -6682,13 +6362,13 @@
         <v>2008</v>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>

--- a/docs/lacunas_tecnicos_formacoes_2008_2013.xlsx
+++ b/docs/lacunas_tecnicos_formacoes_2008_2013.xlsx
@@ -414,23 +414,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T83"/>
+  <dimension ref="A1:T62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="76" customWidth="1" min="8" max="8"/>
+    <col width="39" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="25" customWidth="1" min="10" max="10"/>
     <col width="25" customWidth="1" min="11" max="11"/>
     <col width="26" customWidth="1" min="12" max="12"/>
     <col width="74" customWidth="1" min="13" max="13"/>
-    <col width="39" customWidth="1" min="14" max="14"/>
+    <col width="37" customWidth="1" min="14" max="14"/>
     <col width="32" customWidth="1" min="15" max="15"/>
     <col width="33" customWidth="1" min="16" max="16"/>
     <col width="33" customWidth="1" min="17" max="17"/>
@@ -813,11 +813,19 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>tecnico_mandante, tecnico_visitante, formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>formacao_mandante, formacao_visitante</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Ney Franco</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Cuca</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
@@ -922,24 +930,24 @@
         <v>2009</v>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C7" t="n">
-        <v>2862</v>
+        <v>2908</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2009-08-02</t>
+          <t>2009-08-22</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Athletico-PR</t>
+          <t>Santo Andre</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -949,43 +957,43 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>formacao_mandante, formacao_visitante</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Alexandre Gallo</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Ney Franco</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/965902</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>tecnico_mandante, tecnico_visitante</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>3-5-2</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>3-5-2</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/939223</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>3-5-2</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>3-5-2</t>
-        </is>
-      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Alexandre Gallo</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ney Franco</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
@@ -999,32 +1007,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>2908</v>
+        <v>3099</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2009-08-22</t>
+          <t>2010-05-15</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Santo Andre</t>
+          <t>Vitoria</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1034,19 +1042,19 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Alexandre Gallo</t>
+          <t>Ricardo Silva</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Ney Franco</t>
+          <t>Rogério Lourenço</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/965902</t>
+          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1003486</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1056,12 +1064,12 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Alexandre Gallo</t>
+          <t>Ricardo Silva</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ney Franco</t>
+          <t>Rogério Lourenço</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -1082,14 +1090,14 @@
         <v>2010</v>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="C9" t="n">
-        <v>3099</v>
+        <v>3443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2010-05-15</t>
+          <t>2010-11-21</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1099,7 +1107,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1114,19 +1122,19 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Ricardo Silva</t>
+          <t>Antônio Lopes</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Rogério Lourenço</t>
+          <t>Tite</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1003486</t>
+          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1009448</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1136,12 +1144,12 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Ricardo Silva</t>
+          <t>Antônio Lopes</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rogério Lourenço</t>
+          <t>Tite</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
@@ -1162,70 +1170,70 @@
         <v>2010</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>3223</v>
+        <v>3445</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2010-08-15</t>
+          <t>2010-11-21</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gremio Prudente</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vasco</t>
+          <t>Atletico-GO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t>formacao_mandante, formacao_visitante</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Vágner Benazzi</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Renê Simões</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1009449</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>tecnico_mandante, tecnico_visitante</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1006345</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Vágner Benazzi</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Renê Simões</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
@@ -1242,70 +1250,70 @@
         <v>2010</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="C11" t="n">
-        <v>3287</v>
+        <v>3456</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2010-09-11</t>
+          <t>2010-11-28</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitoria</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>formacao_mandante, formacao_visitante</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Vágner Benazzi</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Marcelo Martelotte</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1009459</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
           <t>tecnico_mandante, tecnico_visitante</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1007650</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Vágner Benazzi</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Marcelo Martelotte</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
@@ -1322,14 +1330,14 @@
         <v>2010</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="C12" t="n">
-        <v>3326</v>
+        <v>3466</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2010-09-23</t>
+          <t>2010-12-05</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1339,53 +1347,53 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Atletico-GO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
+          <t>formacao_mandante, formacao_visitante</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Antônio Lopes</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Renê Simões</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1009468</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
           <t>tecnico_mandante, tecnico_visitante</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1009327</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Antônio Lopes</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Renê Simões</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
@@ -1399,73 +1407,73 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B13" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>3333</v>
+        <v>3467</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2010-09-26</t>
+          <t>2011-05-21</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vitoria</t>
+          <t>Atletico-MG</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Athletico-PR</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
+          <t>formacao_mandante, formacao_visitante</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Dorival Júnior</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Adilson Batista</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1091614</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
           <t>tecnico_mandante, tecnico_visitante</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1009337</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Dorival Júnior</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Adilson Batista</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
@@ -1479,73 +1487,73 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B14" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>3340</v>
+        <v>3504</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2010-09-29</t>
+          <t>2011-06-12</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gremio Prudente</t>
+          <t>Atletico-GO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ceara</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4-2</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
+          <t>formacao_mandante, formacao_visitante</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Paulo César Gusmão</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Vagner Mancini</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1093666</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
           <t>tecnico_mandante, tecnico_visitante</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>4-5-1</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1009343</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>4-5-1</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Paulo César Gusmão</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Vagner Mancini</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
@@ -1559,17 +1567,17 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B15" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>3342</v>
+        <v>3579</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2010-09-29</t>
+          <t>2011-07-23</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1579,53 +1587,53 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitoria</t>
+          <t>Botafogo-RJ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
+          <t>formacao_mandante, formacao_visitante</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Renato Gaúcho</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Caio Júnior</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1093731</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
           <t>tecnico_mandante, tecnico_visitante</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1009348</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Renato Gaúcho</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Caio Júnior</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
@@ -1639,73 +1647,73 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B16" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C16" t="n">
-        <v>3350</v>
+        <v>3804</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2010-10-02</t>
+          <t>2011-11-13</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gremio Prudente</t>
+          <t>Vasco</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Botafogo-RJ</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
+          <t>formacao_mandante, formacao_visitante</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Cristóvão Borges</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Caio Júnior</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1164795</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
           <t>tecnico_mandante, tecnico_visitante</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1009353</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Cristóvão Borges</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Caio Júnior</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
@@ -1719,17 +1727,17 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2010</v>
+        <v>2013</v>
       </c>
       <c r="B17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C17" t="n">
-        <v>3351</v>
+        <v>4498</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2010-10-02</t>
+          <t>2013-10-12</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1739,252 +1747,204 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gremio</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>tecnico_mandante, tecnico_visitante</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1009357</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
+          <t>formacao_mandante, formacao_visitante</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Ney Franco</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Péricles Chamusca</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>Link conhecido; conferir/aplicar somente os campos listados em o_que_falta.</t>
+          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2010</v>
+        <v>2013</v>
       </c>
       <c r="B18" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C18" t="n">
-        <v>3355</v>
+        <v>4516</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2010-10-02</t>
+          <t>2013-10-17</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Vitoria</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sao Paulo</t>
+          <t>Botafogo-RJ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>tecnico_mandante, tecnico_visitante</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>4-5-1</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1009358</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
+          <t>formacao_mandante, formacao_visitante</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Ney Franco</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Oswaldo de Oliveira</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>4-5-1</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>Link conhecido; conferir/aplicar somente os campos listados em o_que_falta.</t>
+          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2010</v>
+        <v>2013</v>
       </c>
       <c r="B19" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C19" t="n">
-        <v>3362</v>
+        <v>4521</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2010-10-06</t>
+          <t>2013-10-20</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>Sao Paulo</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Vitoria</t>
-        </is>
-      </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>tecnico_mandante, tecnico_visitante</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>4-5-1</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1009359</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
+          <t>formacao_mandante, formacao_visitante</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Cristóvão Borges</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Muricy Ramalho</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>4-5-1</t>
-        </is>
-      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>Link conhecido; conferir/aplicar somente os campos listados em o_que_falta.</t>
+          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2010</v>
+        <v>2013</v>
       </c>
       <c r="B20" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C20" t="n">
-        <v>3443</v>
+        <v>4522</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2010-11-21</t>
+          <t>2013-10-20</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vitoria</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Athletico-PR</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1994,77 +1954,61 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Antônio Lopes</t>
+          <t>Enderson Moreira</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Tite</t>
+          <t>Vagner Mancini</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1009448</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>tecnico_mandante, tecnico_visitante</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>Antônio Lopes</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Tite</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>Link conhecido; conferir/aplicar somente os campos listados em o_que_falta.</t>
+          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2010</v>
+        <v>2013</v>
       </c>
       <c r="B21" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C21" t="n">
-        <v>3445</v>
+        <v>4524</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2010-11-21</t>
+          <t>2013-10-20</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Botafogo-RJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Atletico-GO</t>
+          <t>Vasco</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2074,77 +2018,61 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Vágner Benazzi</t>
+          <t>Oswaldo de Oliveira</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Renê Simões</t>
+          <t>Dorival Júnior</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1009449</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>tecnico_mandante, tecnico_visitante</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Vágner Benazzi</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Renê Simões</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>Link conhecido; conferir/aplicar somente os campos listados em o_que_falta.</t>
+          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2010</v>
+        <v>2013</v>
       </c>
       <c r="B22" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C22" t="n">
-        <v>3456</v>
+        <v>4525</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2010-11-28</t>
+          <t>2013-10-20</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2154,77 +2082,61 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Vágner Benazzi</t>
+          <t>Péricles Chamusca</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Marcelo Martelotte</t>
+          <t>Marcelo Oliveira</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1009459</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>tecnico_mandante, tecnico_visitante</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Vágner Benazzi</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Marcelo Martelotte</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>Link conhecido; conferir/aplicar somente os campos listados em o_que_falta.</t>
+          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2010</v>
+        <v>2013</v>
       </c>
       <c r="B23" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C23" t="n">
-        <v>3466</v>
+        <v>4527</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2010-12-05</t>
+          <t>2013-10-26</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vitoria</t>
+          <t>Botafogo-RJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atletico-GO</t>
+          <t>Atletico-MG</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2234,77 +2146,61 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Antônio Lopes</t>
+          <t>Oswaldo de Oliveira</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Renê Simões</t>
+          <t>Cuca</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1009468</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>tecnico_mandante, tecnico_visitante</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Antônio Lopes</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Renê Simões</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>Link conhecido; conferir/aplicar somente os campos listados em o_que_falta.</t>
+          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="C24" t="n">
-        <v>3467</v>
+        <v>4528</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2011-05-21</t>
+          <t>2013-10-26</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Atletico-MG</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Athletico-PR</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>5-3</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2314,77 +2210,61 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Dorival Júnior</t>
+          <t>Marcelo Oliveira</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Adilson Batista</t>
+          <t>Argel Fuchs</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1091614</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>tecnico_mandante, tecnico_visitante</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Dorival Júnior</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Adilson Batista</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>Link conhecido; conferir/aplicar somente os campos listados em o_que_falta.</t>
+          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="C25" t="n">
-        <v>3504</v>
+        <v>4529</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2011-06-12</t>
+          <t>2013-10-27</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Atletico-GO</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ceara</t>
+          <t>Athletico-PR</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2394,7 +2274,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Paulo César Gusmão</t>
+          <t>Cristóvão Borges</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2404,307 +2284,243 @@
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1093666</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>tecnico_mandante, tecnico_visitante</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>Paulo César Gusmão</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Vagner Mancini</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>Link conhecido; conferir/aplicar somente os campos listados em o_que_falta.</t>
+          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="B26" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="C26" t="n">
-        <v>3535</v>
+        <v>4531</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2011-06-30</t>
+          <t>2013-10-27</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Athletico-PR</t>
+          <t>Sao Paulo</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>tecnico_mandante, tecnico_visitante</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>4-5-1</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>4-5-1</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1093700</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
+          <t>formacao_mandante, formacao_visitante</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Clemer</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Muricy Ramalho</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>4-5-1</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>4-5-1</t>
-        </is>
-      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>Link conhecido; conferir/aplicar somente os campos listados em o_que_falta.</t>
+          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="B27" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C27" t="n">
-        <v>3548</v>
+        <v>4533</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2011-07-09</t>
+          <t>2013-10-27</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sao Paulo</t>
+          <t>Portuguesa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>tecnico_mandante, tecnico_visitante</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>4-5-1</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1093712</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
+          <t>formacao_mandante, formacao_visitante</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Guto Ferreira</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Jayme de Almeida Filho</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>4-5-1</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>Link conhecido; conferir/aplicar somente os campos listados em o_que_falta.</t>
+          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="B28" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C28" t="n">
-        <v>3577</v>
+        <v>4535</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2011-07-21</t>
+          <t>2013-10-27</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Vitoria</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>tecnico_mandante, tecnico_visitante</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>3-5-2</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1093734</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
+          <t>formacao_mandante, formacao_visitante</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Vanderlei Luxemburgo</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Ney Franco</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>3-5-2</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>Link conhecido; conferir/aplicar somente os campos listados em o_que_falta.</t>
+          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="B29" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C29" t="n">
-        <v>3579</v>
+        <v>4536</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2011-07-23</t>
+          <t>2013-10-27</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Athletico-PR</t>
+          <t>Nautico</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Botafogo-RJ</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2714,152 +2530,120 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Renato Gaúcho</t>
+          <t>Marcelo Martelotte</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Caio Júnior</t>
+          <t>Enderson Moreira</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1093731</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>tecnico_mandante, tecnico_visitante</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>Renato Gaúcho</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Caio Júnior</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>Link conhecido; conferir/aplicar somente os campos listados em o_que_falta.</t>
+          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="B30" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="C30" t="n">
-        <v>3592</v>
+        <v>4537</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2011-07-31</t>
+          <t>2013-11-02</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Sao Paulo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Atletico-GO</t>
+          <t>Portuguesa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>tecnico_mandante, tecnico_visitante</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>4-5-1</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1093757</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
+          <t>formacao_mandante, formacao_visitante</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Muricy Ramalho</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Guto Ferreira</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>4-5-1</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>Link conhecido; conferir/aplicar somente os campos listados em o_que_falta.</t>
+          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="B31" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C31" t="n">
-        <v>3614</v>
+        <v>4538</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2011-08-07</t>
+          <t>2013-11-02</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Vasco</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Atletico-GO</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2869,242 +2653,194 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>tecnico_mandante, tecnico_visitante</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1093780</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
+          <t>formacao_mandante, formacao_visitante</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Adilson Batista</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Péricles Chamusca</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>Link conhecido; conferir/aplicar somente os campos listados em o_que_falta.</t>
+          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="B32" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C32" t="n">
-        <v>3618</v>
+        <v>4539</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2011-08-13</t>
+          <t>2013-11-02</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atletico-GO</t>
+          <t>Atletico-MG</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Nautico</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>tecnico_mandante, tecnico_visitante</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1093782</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
+          <t>formacao_mandante, formacao_visitante</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Cuca</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Marcelo Martelotte</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>Link conhecido; conferir/aplicar somente os campos listados em o_que_falta.</t>
+          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="B33" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>3772</v>
+        <v>4540</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2011-10-23</t>
+          <t>2013-11-03</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sao Paulo</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Botafogo-RJ</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>tecnico_mandante, tecnico_visitante</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1158419</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
+          <t>formacao_mandante, formacao_visitante</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Enderson Moreira</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Oswaldo de Oliveira</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>4-4-2</t>
-        </is>
-      </c>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>Link conhecido; conferir/aplicar somente os campos listados em o_que_falta.</t>
+          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="B34" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C34" t="n">
-        <v>3804</v>
+        <v>4542</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2011-11-13</t>
+          <t>2013-11-03</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vasco</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Botafogo-RJ</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3114,126 +2850,94 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Cristóvão Borges</t>
+          <t>Claudinei Oliveira</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Caio Júnior</t>
+          <t>Marcelo Oliveira</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/1164795</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>tecnico_mandante, tecnico_visitante</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>Cristóvão Borges</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Caio Júnior</t>
-        </is>
-      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>Link conhecido; conferir/aplicar somente os campos listados em o_que_falta.</t>
+          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="B35" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C35" t="n">
-        <v>4223</v>
+        <v>4543</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2012-12-02</t>
+          <t>2013-11-03</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Vitoria</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>tecnico_mandante, tecnico_visitante</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>4-2-3-1</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>4-4-2 duplo 6</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>https://www.transfermarkt.com.br/spielbericht/index/spielbericht/2206691</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
+          <t>formacao_mandante, formacao_visitante</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Ney Franco</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Tite</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>4-2-3-1</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>4-4-2 duplo 6</t>
-        </is>
-      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr">
         <is>
-          <t>Transfermarkt linkado; ogol se Transfermarkt nao trouxer o campo</t>
+          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>Link conhecido; conferir/aplicar somente os campos listados em o_que_falta.</t>
+          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
         </is>
       </c>
     </row>
@@ -3242,29 +2946,29 @@
         <v>2013</v>
       </c>
       <c r="B36" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C36" t="n">
-        <v>4498</v>
+        <v>4544</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2013-10-12</t>
+          <t>2013-11-03</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vitoria</t>
+          <t>Athletico-PR</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3274,12 +2978,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Ney Franco</t>
+          <t>Vagner Mancini</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Péricles Chamusca</t>
+          <t>Clemer</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -3306,48 +3010,48 @@
         <v>2013</v>
       </c>
       <c r="B37" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C37" t="n">
-        <v>4508</v>
+        <v>4545</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2013-10-16</t>
+          <t>2013-11-03</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>tecnico_mandante, tecnico_visitante</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>4-3-3 defensivo</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>4-5-1</t>
-        </is>
-      </c>
+          <t>formacao_mandante, formacao_visitante</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Argel Fuchs</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Jorginho</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
@@ -3370,48 +3074,48 @@
         <v>2013</v>
       </c>
       <c r="B38" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C38" t="n">
-        <v>4509</v>
+        <v>4546</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2013-10-16</t>
+          <t>2013-11-03</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Portuguesa</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>tecnico_mandante, tecnico_visitante</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>4-1-3-2</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>4-4-2 duplo 6</t>
-        </is>
-      </c>
+          <t>formacao_mandante, formacao_visitante</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Jayme de Almeida Filho</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Vanderlei Luxemburgo</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
@@ -3434,29 +3138,29 @@
         <v>2013</v>
       </c>
       <c r="B39" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C39" t="n">
-        <v>4516</v>
+        <v>4557</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2013-10-17</t>
+          <t>2013-11-13</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Vitoria</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Botafogo-RJ</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3466,12 +3170,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Ney Franco</t>
+          <t>Enderson Moreira</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Oswaldo de Oliveira</t>
+          <t>Jorginho</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -3498,29 +3202,29 @@
         <v>2013</v>
       </c>
       <c r="B40" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C40" t="n">
-        <v>4521</v>
+        <v>4559</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2013-10-20</t>
+          <t>2013-11-13</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Botafogo-RJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sao Paulo</t>
+          <t>Portuguesa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3530,12 +3234,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Cristóvão Borges</t>
+          <t>Oswaldo de Oliveira</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Muricy Ramalho</t>
+          <t>Guto Ferreira</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -3562,19 +3266,19 @@
         <v>2013</v>
       </c>
       <c r="B41" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C41" t="n">
-        <v>4522</v>
+        <v>4560</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2013-10-20</t>
+          <t>2013-11-13</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3584,7 +3288,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3594,7 +3298,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Enderson Moreira</t>
+          <t>Argel Fuchs</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3626,29 +3330,29 @@
         <v>2013</v>
       </c>
       <c r="B42" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C42" t="n">
-        <v>4524</v>
+        <v>4561</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2013-10-20</t>
+          <t>2013-11-13</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Botafogo-RJ</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vasco</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3658,12 +3362,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Oswaldo de Oliveira</t>
+          <t>Péricles Chamusca</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Dorival Júnior</t>
+          <t>Tite</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3690,29 +3394,29 @@
         <v>2013</v>
       </c>
       <c r="B43" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C43" t="n">
-        <v>4525</v>
+        <v>4562</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2013-10-20</t>
+          <t>2013-11-13</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Sao Paulo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3722,12 +3426,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Péricles Chamusca</t>
+          <t>Muricy Ramalho</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Marcelo Oliveira</t>
+          <t>Jayme de Almeida Filho</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3754,29 +3458,29 @@
         <v>2013</v>
       </c>
       <c r="B44" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C44" t="n">
-        <v>4527</v>
+        <v>4563</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2013-10-26</t>
+          <t>2013-11-13</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Botafogo-RJ</t>
+          <t>Vitoria</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Atletico-MG</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3786,12 +3490,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Oswaldo de Oliveira</t>
+          <t>Ney Franco</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Cuca</t>
+          <t>Marcelo Oliveira</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3818,29 +3522,29 @@
         <v>2013</v>
       </c>
       <c r="B45" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C45" t="n">
-        <v>4528</v>
+        <v>4564</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2013-10-26</t>
+          <t>2013-11-14</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>5-3</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3850,12 +3554,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Marcelo Oliveira</t>
+          <t>Claudinei Oliveira</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Argel Fuchs</t>
+          <t>Cristóvão Borges</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3882,29 +3586,29 @@
         <v>2013</v>
       </c>
       <c r="B46" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C46" t="n">
-        <v>4529</v>
+        <v>4565</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2013-10-27</t>
+          <t>2013-11-14</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Atletico-MG</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Athletico-PR</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3914,12 +3618,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Cristóvão Borges</t>
+          <t>Cuca</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Vagner Mancini</t>
+          <t>Clemer</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3946,29 +3650,29 @@
         <v>2013</v>
       </c>
       <c r="B47" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C47" t="n">
-        <v>4531</v>
+        <v>4566</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2013-10-27</t>
+          <t>2013-11-14</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sao Paulo</t>
+          <t>Nautico</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3978,12 +3682,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Clemer</t>
+          <t>Dorival Júnior</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Muricy Ramalho</t>
+          <t>Marcelo Martelotte</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -4010,29 +3714,29 @@
         <v>2013</v>
       </c>
       <c r="B48" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C48" t="n">
-        <v>4533</v>
+        <v>4567</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2013-10-27</t>
+          <t>2013-11-16</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Portuguesa</t>
+          <t>Botafogo-RJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Athletico-PR</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>4-0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4042,12 +3746,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Guto Ferreira</t>
+          <t>Oswaldo de Oliveira</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Jayme de Almeida Filho</t>
+          <t>Vagner Mancini</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -4074,29 +3778,29 @@
         <v>2013</v>
       </c>
       <c r="B49" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C49" t="n">
-        <v>4535</v>
+        <v>4568</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2013-10-27</t>
+          <t>2013-11-16</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitoria</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4106,12 +3810,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Vanderlei Luxemburgo</t>
+          <t>Péricles Chamusca</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Ney Franco</t>
+          <t>Argel Fuchs</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -4138,29 +3842,29 @@
         <v>2013</v>
       </c>
       <c r="B50" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C50" t="n">
-        <v>4536</v>
+        <v>4569</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2013-10-27</t>
+          <t>2013-11-17</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Nautico</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Vasco</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4170,12 +3874,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Marcelo Martelotte</t>
+          <t>Tite</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Enderson Moreira</t>
+          <t>Adilson Batista</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -4202,29 +3906,29 @@
         <v>2013</v>
       </c>
       <c r="B51" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C51" t="n">
-        <v>4537</v>
+        <v>4570</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2013-11-02</t>
+          <t>2013-11-17</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sao Paulo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Portuguesa</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4234,12 +3938,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Muricy Ramalho</t>
+          <t>Marcelo Oliveira</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Guto Ferreira</t>
+          <t>Jorginho</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -4266,24 +3970,24 @@
         <v>2013</v>
       </c>
       <c r="B52" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C52" t="n">
-        <v>4538</v>
+        <v>4571</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2013-11-02</t>
+          <t>2013-11-17</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Vasco</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Sao Paulo</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4298,12 +4002,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Adilson Batista</t>
+          <t>Dorival Júnior</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Péricles Chamusca</t>
+          <t>Muricy Ramalho</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -4330,29 +4034,29 @@
         <v>2013</v>
       </c>
       <c r="B53" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C53" t="n">
-        <v>4539</v>
+        <v>4572</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2013-11-02</t>
+          <t>2013-11-17</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Atletico-MG</t>
+          <t>Vitoria</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nautico</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4362,12 +4066,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Cuca</t>
+          <t>Ney Franco</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Marcelo Martelotte</t>
+          <t>Claudinei Oliveira</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -4394,14 +4098,14 @@
         <v>2013</v>
       </c>
       <c r="B54" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C54" t="n">
-        <v>4540</v>
+        <v>4573</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2013-11-03</t>
+          <t>2013-11-17</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -4411,12 +4115,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Botafogo-RJ</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4431,7 +4135,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Oswaldo de Oliveira</t>
+          <t>Clemer</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -4458,24 +4162,24 @@
         <v>2013</v>
       </c>
       <c r="B55" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C55" t="n">
-        <v>4542</v>
+        <v>4575</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2013-11-03</t>
+          <t>2013-11-17</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Nautico</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4490,12 +4194,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Claudinei Oliveira</t>
+          <t>Marcelo Martelotte</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Marcelo Oliveira</t>
+          <t>Cristóvão Borges</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -4522,29 +4226,29 @@
         <v>2013</v>
       </c>
       <c r="B56" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C56" t="n">
-        <v>4543</v>
+        <v>4576</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2013-11-03</t>
+          <t>2013-11-17</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Vitoria</t>
+          <t>Portuguesa</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Atletico-MG</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4554,12 +4258,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Ney Franco</t>
+          <t>Guto Ferreira</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Tite</t>
+          <t>Cuca</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -4586,29 +4290,29 @@
         <v>2013</v>
       </c>
       <c r="B57" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C57" t="n">
-        <v>4544</v>
+        <v>4577</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2013-11-03</t>
+          <t>2013-11-23</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Athletico-PR</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Vitoria</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4618,12 +4322,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Vagner Mancini</t>
+          <t>Argel Fuchs</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Clemer</t>
+          <t>Ney Franco</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -4650,29 +4354,29 @@
         <v>2013</v>
       </c>
       <c r="B58" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C58" t="n">
-        <v>4545</v>
+        <v>4578</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2013-11-03</t>
+          <t>2013-11-23</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Vasco</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4682,12 +4386,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Argel Fuchs</t>
+          <t>Adilson Batista</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Jorginho</t>
+          <t>Marcelo Oliveira</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -4714,29 +4418,29 @@
         <v>2013</v>
       </c>
       <c r="B59" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C59" t="n">
-        <v>4546</v>
+        <v>4580</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2013-11-03</t>
+          <t>2013-11-24</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Athletico-PR</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Nautico</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>6-1</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4746,12 +4450,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Jayme de Almeida Filho</t>
+          <t>Vagner Mancini</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Vanderlei Luxemburgo</t>
+          <t>Marcelo Martelotte</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4778,29 +4482,29 @@
         <v>2013</v>
       </c>
       <c r="B60" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C60" t="n">
-        <v>4557</v>
+        <v>4590</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2013-11-13</t>
+          <t>2013-12-01</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Sao Paulo</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4810,12 +4514,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Enderson Moreira</t>
+          <t>Argel Fuchs</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Jorginho</t>
+          <t>Muricy Ramalho</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4842,29 +4546,29 @@
         <v>2013</v>
       </c>
       <c r="B61" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C61" t="n">
-        <v>4559</v>
+        <v>4591</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2013-11-13</t>
+          <t>2013-12-01</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Botafogo-RJ</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Portuguesa</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4874,12 +4578,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Oswaldo de Oliveira</t>
+          <t>Marcelo Oliveira</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Guto Ferreira</t>
+          <t>Cristóvão Borges</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4906,29 +4610,29 @@
         <v>2013</v>
       </c>
       <c r="B62" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C62" t="n">
-        <v>4560</v>
+        <v>4594</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2013-11-13</t>
+          <t>2013-12-01</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Vitoria</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Athletico-PR</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4938,12 +4642,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Argel Fuchs</t>
+          <t>Ney Franco</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Vagner Mancini</t>
+          <t>Jayme de Almeida Filho</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4960,1350 +4664,6 @@
         </is>
       </c>
       <c r="T62" t="inlineStr">
-        <is>
-          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B63" t="n">
-        <v>34</v>
-      </c>
-      <c r="C63" t="n">
-        <v>4561</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>2013-11-13</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Coritiba</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Corinthians</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>Péricles Chamusca</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>Tite</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
-        </is>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B64" t="n">
-        <v>34</v>
-      </c>
-      <c r="C64" t="n">
-        <v>4562</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>2013-11-13</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Flamengo</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>2-0</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Muricy Ramalho</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>Jayme de Almeida Filho</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
-        </is>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B65" t="n">
-        <v>34</v>
-      </c>
-      <c r="C65" t="n">
-        <v>4563</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>2013-11-13</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Vitoria</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Cruzeiro</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>1-3</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>Ney Franco</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>Marcelo Oliveira</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
-        </is>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B66" t="n">
-        <v>34</v>
-      </c>
-      <c r="C66" t="n">
-        <v>4564</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>2013-11-14</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Santos</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Bahia</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>3-0</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>Claudinei Oliveira</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>Cristóvão Borges</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
-        </is>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B67" t="n">
-        <v>34</v>
-      </c>
-      <c r="C67" t="n">
-        <v>4565</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>2013-11-14</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Atletico-MG</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Internacional</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>2-1</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>Cuca</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>Clemer</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
-        </is>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B68" t="n">
-        <v>34</v>
-      </c>
-      <c r="C68" t="n">
-        <v>4566</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>2013-11-14</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Fluminense</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Nautico</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>2-0</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>Dorival Júnior</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>Marcelo Martelotte</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr"/>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
-        </is>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B69" t="n">
-        <v>35</v>
-      </c>
-      <c r="C69" t="n">
-        <v>4567</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>2013-11-16</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Botafogo-RJ</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Athletico-PR</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>4-0</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>Oswaldo de Oliveira</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>Vagner Mancini</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr"/>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
-        </is>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B70" t="n">
-        <v>35</v>
-      </c>
-      <c r="C70" t="n">
-        <v>4568</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>2013-11-16</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Coritiba</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Criciuma</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>1-2</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>Péricles Chamusca</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>Argel Fuchs</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr"/>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
-        </is>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B71" t="n">
-        <v>35</v>
-      </c>
-      <c r="C71" t="n">
-        <v>4569</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>2013-11-17</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Corinthians</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Vasco</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Tite</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>Adilson Batista</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="inlineStr"/>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
-        </is>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B72" t="n">
-        <v>35</v>
-      </c>
-      <c r="C72" t="n">
-        <v>4570</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>2013-11-17</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Cruzeiro</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Ponte Preta</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>2-2</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>Marcelo Oliveira</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>Jorginho</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="inlineStr"/>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
-        </is>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B73" t="n">
-        <v>35</v>
-      </c>
-      <c r="C73" t="n">
-        <v>4571</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>2013-11-17</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Fluminense</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>2-1</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>Dorival Júnior</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>Muricy Ramalho</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr"/>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
-        </is>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B74" t="n">
-        <v>35</v>
-      </c>
-      <c r="C74" t="n">
-        <v>4572</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>2013-11-17</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Vitoria</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Santos</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>2-0</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>Ney Franco</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>Claudinei Oliveira</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
-        </is>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B75" t="n">
-        <v>35</v>
-      </c>
-      <c r="C75" t="n">
-        <v>4573</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>2013-11-17</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Goias</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Internacional</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>3-1</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>Enderson Moreira</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>Clemer</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr"/>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
-        </is>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B76" t="n">
-        <v>35</v>
-      </c>
-      <c r="C76" t="n">
-        <v>4575</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>2013-11-17</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Nautico</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Bahia</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>Marcelo Martelotte</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>Cristóvão Borges</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr"/>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
-        </is>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B77" t="n">
-        <v>35</v>
-      </c>
-      <c r="C77" t="n">
-        <v>4576</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>2013-11-17</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Portuguesa</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Atletico-MG</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>2-0</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>Guto Ferreira</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>Cuca</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr"/>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
-        </is>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B78" t="n">
-        <v>36</v>
-      </c>
-      <c r="C78" t="n">
-        <v>4577</v>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>2013-11-23</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Criciuma</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Vitoria</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>Argel Fuchs</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>Ney Franco</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="inlineStr"/>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
-        </is>
-      </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B79" t="n">
-        <v>36</v>
-      </c>
-      <c r="C79" t="n">
-        <v>4578</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>2013-11-23</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Vasco</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Cruzeiro</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>2-1</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>Adilson Batista</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>Marcelo Oliveira</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr"/>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
-        </is>
-      </c>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B80" t="n">
-        <v>36</v>
-      </c>
-      <c r="C80" t="n">
-        <v>4580</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>2013-11-24</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Athletico-PR</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Nautico</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>6-1</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>Vagner Mancini</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>Marcelo Martelotte</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr"/>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
-        </is>
-      </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B81" t="n">
-        <v>37</v>
-      </c>
-      <c r="C81" t="n">
-        <v>4590</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>2013-12-01</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Criciuma</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>Argel Fuchs</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>Muricy Ramalho</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr"/>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
-        </is>
-      </c>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B82" t="n">
-        <v>37</v>
-      </c>
-      <c r="C82" t="n">
-        <v>4591</v>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>2013-12-01</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Cruzeiro</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Bahia</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>1-2</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>Marcelo Oliveira</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>Cristóvão Borges</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr"/>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
-        </is>
-      </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B83" t="n">
-        <v>37</v>
-      </c>
-      <c r="C83" t="n">
-        <v>4594</v>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>2013-12-01</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Vitoria</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Flamengo</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>4-2</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>formacao_mandante, formacao_visitante</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>Ney Franco</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>Jayme de Almeida Filho</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr"/>
-      <c r="R83" t="inlineStr"/>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>Transfermarkt buscar por jogo; ogol; ESPN/arquivo local como fallback</t>
-        </is>
-      </c>
-      <c r="T83" t="inlineStr">
         <is>
           <t>Sem link direto auditado; procurar por temporada, rodada, times, placar e data do banco.</t>
         </is>
@@ -6320,7 +4680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -6379,13 +4739,13 @@
         <v>2009</v>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -6396,13 +4756,13 @@
         <v>2010</v>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -6413,13 +4773,13 @@
         <v>2011</v>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -6427,36 +4787,19 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>92</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B7" t="n">
-        <v>48</v>
-      </c>
-      <c r="C7" t="n">
-        <v>96</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
